--- a/sample-data/import/articles-import-test.xlsx
+++ b/sample-data/import/articles-import-test.xlsx
@@ -1110,7 +1110,7 @@
         <v>120</v>
       </c>
       <c r="L16">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M16" t="str">
         <v/>
@@ -1286,7 +1286,7 @@
         <v>100</v>
       </c>
       <c r="L20">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M20" t="str">
         <v/>
